--- a/测试数据-课堂演示/excel/9-宏观支撑矩阵导入.xlsx
+++ b/测试数据-课堂演示/excel/9-宏观支撑矩阵导入.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宏观支撑矩阵导入" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,30 +415,24 @@
   </sheetPr>
   <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>专业代码*</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>课程代码*</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>指标点编号*</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>宏观总支撑权重*</t>
         </is>
@@ -468,13 +449,11 @@
           <t>SE101</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0853</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="3">
@@ -488,13 +467,11 @@
           <t>SE101</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2816</v>
+        <v>0.3567</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +485,11 @@
           <t>SE101</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
+      <c r="C4" t="n">
+        <v>5.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2587</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -528,13 +503,11 @@
           <t>SE101</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3411</v>
+        <v>0.5103</v>
       </c>
     </row>
     <row r="6">
@@ -548,13 +521,11 @@
           <t>SE101</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
+      <c r="C6" t="n">
+        <v>7.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -568,13 +539,11 @@
           <t>SE102</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
+      <c r="C7" t="n">
+        <v>6.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0827</v>
+        <v>0.1298</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +557,11 @@
           <t>SE102</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1.1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.214</v>
+        <v>0.2711</v>
       </c>
     </row>
     <row r="9">
@@ -608,13 +575,11 @@
           <t>SE102</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
+      <c r="C9" t="n">
+        <v>7.1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1995</v>
+        <v>0.4907</v>
       </c>
     </row>
     <row r="10">
@@ -628,13 +593,11 @@
           <t>SE102</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2545</v>
+        <v>0.3853</v>
       </c>
     </row>
     <row r="11">
@@ -648,13 +611,11 @@
           <t>SE102</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2.1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2493</v>
+        <v>0.3625</v>
       </c>
     </row>
     <row r="12">
@@ -668,13 +629,11 @@
           <t>SE103</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
+      <c r="C12" t="n">
+        <v>6.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2921</v>
+        <v>0.4583</v>
       </c>
     </row>
     <row r="13">
@@ -688,13 +647,11 @@
           <t>SE103</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
+      <c r="C13" t="n">
+        <v>2.1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0615</v>
+        <v>0.08939999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -708,13 +665,11 @@
           <t>SE103</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
+      <c r="C14" t="n">
+        <v>3.3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1627</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -728,13 +683,11 @@
           <t>SE103</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
+      <c r="C15" t="n">
+        <v>4.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.107</v>
+        <v>0.2894</v>
       </c>
     </row>
     <row r="16">
@@ -748,13 +701,11 @@
           <t>SE103</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
+      <c r="C16" t="n">
+        <v>2.2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0829</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="17">
@@ -768,13 +719,11 @@
           <t>SE103</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
+      <c r="C17" t="n">
+        <v>1.1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2938</v>
+        <v>0.3722</v>
       </c>
     </row>
     <row r="18">
@@ -788,13 +737,11 @@
           <t>SE104</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
+      <c r="C18" t="n">
+        <v>2.1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2405</v>
+        <v>0.3497</v>
       </c>
     </row>
     <row r="19">
@@ -808,13 +755,11 @@
           <t>SE104</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
+      <c r="C19" t="n">
+        <v>1.2</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1713</v>
+        <v>0.2593</v>
       </c>
     </row>
     <row r="20">
@@ -828,13 +773,11 @@
           <t>SE104</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+      <c r="C20" t="n">
+        <v>3.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.229</v>
+        <v>0.5206</v>
       </c>
     </row>
     <row r="21">
@@ -848,13 +791,11 @@
           <t>SE104</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
+      <c r="C21" t="n">
+        <v>7.1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2071</v>
+        <v>0.5093</v>
       </c>
     </row>
     <row r="22">
@@ -868,13 +809,11 @@
           <t>SE104</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
+      <c r="C22" t="n">
+        <v>3.1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1521</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -888,13 +827,11 @@
           <t>SE105</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
+      <c r="C23" t="n">
+        <v>6.1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3008</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -908,13 +845,11 @@
           <t>SE105</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
+      <c r="C24" t="n">
+        <v>1.2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1229</v>
+        <v>0.1861</v>
       </c>
     </row>
     <row r="25">
@@ -928,13 +863,11 @@
           <t>SE105</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
+      <c r="C25" t="n">
+        <v>4.1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0653</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -948,13 +881,11 @@
           <t>SE105</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
+      <c r="C26" t="n">
+        <v>2.2</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0236</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="27">
@@ -968,13 +899,11 @@
           <t>SE105</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
+      <c r="C27" t="n">
+        <v>5.1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2247</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -988,13 +917,11 @@
           <t>SE105</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
+      <c r="C28" t="n">
+        <v>4.2</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2627</v>
+        <v>0.7106</v>
       </c>
     </row>
     <row r="29">
@@ -1008,13 +935,11 @@
           <t>SE106</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
+      <c r="C29" t="n">
+        <v>1.3</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1427</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1028,13 +953,11 @@
           <t>SE106</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
+      <c r="C30" t="n">
+        <v>6.2</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2625</v>
+        <v>0.4119</v>
       </c>
     </row>
     <row r="31">
@@ -1048,13 +971,11 @@
           <t>SE106</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
+      <c r="C31" t="n">
+        <v>2.1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0512</v>
+        <v>0.07439999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1068,13 +989,11 @@
           <t>SE106</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
+      <c r="C32" t="n">
+        <v>1.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1118</v>
+        <v>0.1693</v>
       </c>
     </row>
     <row r="33">
@@ -1088,13 +1007,11 @@
           <t>SE106</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+      <c r="C33" t="n">
+        <v>3.2</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2109</v>
+        <v>0.4794</v>
       </c>
     </row>
     <row r="34">
@@ -1108,13 +1025,11 @@
           <t>SE106</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
+      <c r="C34" t="n">
+        <v>2.2</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2209</v>
+        <v>0.3304</v>
       </c>
     </row>
   </sheetData>

--- a/测试数据-课堂演示/excel/9-宏观支撑矩阵导入.xlsx
+++ b/测试数据-课堂演示/excel/9-宏观支撑矩阵导入.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宏观支撑矩阵" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,32 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +58,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,621 +446,627 @@
   </sheetPr>
   <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>专业代码*</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>课程代码*</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>指标点编号*</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>宏观总支撑权重*</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SE101</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.124</v>
+      <c r="D2" s="3" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>SE101</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.3567</v>
+      <c r="D3" s="3" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>SE101</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>5.2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>SE101</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.5103</v>
+      <c r="D5" s="3" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>SE101</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>7.2</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>SE102</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>6.2</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.1298</v>
+      <c r="D7" s="3" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>SE102</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.2711</v>
+      <c r="D8" s="3" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>SE102</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>7.1</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.4907</v>
+      <c r="D9" s="3" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>SE102</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.3853</v>
+      <c r="D10" s="3" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>SE102</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.3625</v>
+      <c r="D11" s="3" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>SE103</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>6.2</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.4583</v>
+      <c r="D12" s="3" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>SE103</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.08939999999999999</v>
+      <c r="D13" s="3" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>SE103</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>SE103</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.2894</v>
+      <c r="D15" s="3" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>SE103</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.124</v>
+      <c r="D16" s="3" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>SE103</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.3722</v>
+      <c r="D17" s="3" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>SE104</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.3497</v>
+      <c r="D18" s="3" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>SE104</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.2593</v>
+      <c r="D19" s="3" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>SE104</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.5206</v>
+      <c r="D20" s="3" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>SE104</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="2" t="n">
         <v>7.1</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.5093</v>
+      <c r="D21" s="3" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>SE104</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="2" t="n">
         <v>3.1</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>SE105</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="2" t="n">
         <v>6.1</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>SE105</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.1861</v>
+      <c r="D24" s="3" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>SE105</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>SE105</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.0353</v>
+      <c r="D26" s="3" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>SE105</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="2" t="n">
         <v>5.1</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SE105</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="D28" t="n">
-        <v>0.7106</v>
+      <c r="D28" s="3" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SE106</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>SE106</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="2" t="n">
         <v>6.2</v>
       </c>
-      <c r="D30" t="n">
-        <v>0.4119</v>
+      <c r="D30" s="3" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>SE106</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="D31" t="n">
-        <v>0.07439999999999999</v>
+      <c r="D31" s="3" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>SE106</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.1693</v>
+      <c r="D32" s="3" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>SE106</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="D33" t="n">
-        <v>0.4794</v>
+      <c r="D33" s="3" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>080902SE</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>080902SE</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>SE106</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="D34" t="n">
-        <v>0.3304</v>
+      <c r="D34" s="3" t="n">
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
